--- a/reports/nbeats_prediction_results.xlsx
+++ b/reports/nbeats_prediction_results.xlsx
@@ -511,19 +511,19 @@
         <v>23.4</v>
       </c>
       <c r="G2" t="n">
-        <v>56.30754852294922</v>
+        <v>39.58722686767578</v>
       </c>
       <c r="H2" t="n">
-        <v>56.48448944091797</v>
+        <v>59.52019119262695</v>
       </c>
       <c r="I2" t="n">
-        <v>2537.248291015625</v>
+        <v>2382.173828125</v>
       </c>
       <c r="J2" t="n">
-        <v>53.49288177490234</v>
+        <v>49.94996643066406</v>
       </c>
       <c r="K2" t="n">
-        <v>25.57209205627441</v>
+        <v>32.60894012451172</v>
       </c>
     </row>
     <row r="3">
@@ -546,19 +546,19 @@
         <v>23.5</v>
       </c>
       <c r="G3" t="n">
-        <v>51.93167877197266</v>
+        <v>58.1082763671875</v>
       </c>
       <c r="H3" t="n">
-        <v>58.46515655517578</v>
+        <v>67.18798828125</v>
       </c>
       <c r="I3" t="n">
-        <v>2845.19921875</v>
+        <v>2227.640380859375</v>
       </c>
       <c r="J3" t="n">
-        <v>42.52050399780273</v>
+        <v>49.80117416381836</v>
       </c>
       <c r="K3" t="n">
-        <v>26.82330894470215</v>
+        <v>28.94246864318848</v>
       </c>
     </row>
     <row r="4">
@@ -581,19 +581,19 @@
         <v>22.9</v>
       </c>
       <c r="G4" t="n">
-        <v>55.09148788452148</v>
+        <v>48.78900909423828</v>
       </c>
       <c r="H4" t="n">
-        <v>71.56495666503906</v>
+        <v>67.43144226074219</v>
       </c>
       <c r="I4" t="n">
-        <v>2703.04443359375</v>
+        <v>1837.168579101562</v>
       </c>
       <c r="J4" t="n">
-        <v>53.92378616333008</v>
+        <v>56.25993347167969</v>
       </c>
       <c r="K4" t="n">
-        <v>23.62313652038574</v>
+        <v>22.64511299133301</v>
       </c>
     </row>
     <row r="5">
@@ -616,19 +616,19 @@
         <v>22</v>
       </c>
       <c r="G5" t="n">
-        <v>41.64295196533203</v>
+        <v>52.79923629760742</v>
       </c>
       <c r="H5" t="n">
-        <v>60.08255004882812</v>
+        <v>76.94171905517578</v>
       </c>
       <c r="I5" t="n">
-        <v>1492.14697265625</v>
+        <v>2076.168212890625</v>
       </c>
       <c r="J5" t="n">
-        <v>49.16963958740234</v>
+        <v>62.34806442260742</v>
       </c>
       <c r="K5" t="n">
-        <v>33.14049911499023</v>
+        <v>30.45889091491699</v>
       </c>
     </row>
     <row r="6">
@@ -651,19 +651,19 @@
         <v>21</v>
       </c>
       <c r="G6" t="n">
-        <v>50.89614105224609</v>
+        <v>51.23588562011719</v>
       </c>
       <c r="H6" t="n">
-        <v>50.24392318725586</v>
+        <v>76.10706329345703</v>
       </c>
       <c r="I6" t="n">
-        <v>1496.43212890625</v>
+        <v>1296.419555664062</v>
       </c>
       <c r="J6" t="n">
-        <v>51.6594123840332</v>
+        <v>49.81579208374023</v>
       </c>
       <c r="K6" t="n">
-        <v>22.72770881652832</v>
+        <v>26.72619438171387</v>
       </c>
     </row>
     <row r="7">
@@ -686,19 +686,19 @@
         <v>20</v>
       </c>
       <c r="G7" t="n">
-        <v>43.86260986328125</v>
+        <v>57.15619659423828</v>
       </c>
       <c r="H7" t="n">
-        <v>78.82013702392578</v>
+        <v>76.60755920410156</v>
       </c>
       <c r="I7" t="n">
-        <v>1408.996826171875</v>
+        <v>1429.361572265625</v>
       </c>
       <c r="J7" t="n">
-        <v>49.2513313293457</v>
+        <v>43.31041717529297</v>
       </c>
       <c r="K7" t="n">
-        <v>22.03333854675293</v>
+        <v>19.55473899841309</v>
       </c>
     </row>
     <row r="8">
@@ -721,19 +721,19 @@
         <v>19</v>
       </c>
       <c r="G8" t="n">
-        <v>40.09001159667969</v>
+        <v>51.63566970825195</v>
       </c>
       <c r="H8" t="n">
-        <v>80.57546997070312</v>
+        <v>64.36302947998047</v>
       </c>
       <c r="I8" t="n">
-        <v>1672.991455078125</v>
+        <v>1273.521362304688</v>
       </c>
       <c r="J8" t="n">
-        <v>32.51483917236328</v>
+        <v>35.98403930664062</v>
       </c>
       <c r="K8" t="n">
-        <v>17.84552001953125</v>
+        <v>22.2281551361084</v>
       </c>
     </row>
     <row r="9">
@@ -756,19 +756,19 @@
         <v>18.6</v>
       </c>
       <c r="G9" t="n">
-        <v>46.63574600219727</v>
+        <v>55.3524169921875</v>
       </c>
       <c r="H9" t="n">
-        <v>65.00659942626953</v>
+        <v>50.62129592895508</v>
       </c>
       <c r="I9" t="n">
-        <v>857.9415283203125</v>
+        <v>839.0248413085938</v>
       </c>
       <c r="J9" t="n">
-        <v>40.97066879272461</v>
+        <v>38.55916595458984</v>
       </c>
       <c r="K9" t="n">
-        <v>13.71282196044922</v>
+        <v>18.53971481323242</v>
       </c>
     </row>
     <row r="10">
@@ -791,19 +791,19 @@
         <v>18.9</v>
       </c>
       <c r="G10" t="n">
-        <v>55.86869430541992</v>
+        <v>56.25220489501953</v>
       </c>
       <c r="H10" t="n">
-        <v>67.27167510986328</v>
+        <v>77.47187042236328</v>
       </c>
       <c r="I10" t="n">
-        <v>1164.135620117188</v>
+        <v>2057.587890625</v>
       </c>
       <c r="J10" t="n">
-        <v>26.83393478393555</v>
+        <v>46.10461044311523</v>
       </c>
       <c r="K10" t="n">
-        <v>22.10876274108887</v>
+        <v>14.25260543823242</v>
       </c>
     </row>
     <row r="11">
@@ -826,19 +826,19 @@
         <v>19.8</v>
       </c>
       <c r="G11" t="n">
-        <v>49.79767990112305</v>
+        <v>51.49188232421875</v>
       </c>
       <c r="H11" t="n">
-        <v>68.51962280273438</v>
+        <v>74.57093811035156</v>
       </c>
       <c r="I11" t="n">
-        <v>1709.052856445312</v>
+        <v>1267.251342773438</v>
       </c>
       <c r="J11" t="n">
-        <v>48.2940559387207</v>
+        <v>41.07585525512695</v>
       </c>
       <c r="K11" t="n">
-        <v>17.77501487731934</v>
+        <v>18.55783653259277</v>
       </c>
     </row>
     <row r="12">
@@ -861,19 +861,19 @@
         <v>24.2</v>
       </c>
       <c r="G12" t="n">
-        <v>44.44648742675781</v>
+        <v>54.42082214355469</v>
       </c>
       <c r="H12" t="n">
-        <v>70.60556793212891</v>
+        <v>67.63888549804688</v>
       </c>
       <c r="I12" t="n">
-        <v>1554.05078125</v>
+        <v>1861.104858398438</v>
       </c>
       <c r="J12" t="n">
-        <v>32.84084320068359</v>
+        <v>49.34075546264648</v>
       </c>
       <c r="K12" t="n">
-        <v>19.20673179626465</v>
+        <v>16.6522331237793</v>
       </c>
     </row>
     <row r="13">
@@ -896,19 +896,19 @@
         <v>30.8</v>
       </c>
       <c r="G13" t="n">
-        <v>66.50155639648438</v>
+        <v>52.6632080078125</v>
       </c>
       <c r="H13" t="n">
-        <v>55.25530624389648</v>
+        <v>58.63094329833984</v>
       </c>
       <c r="I13" t="n">
-        <v>892.3607177734375</v>
+        <v>1519.304565429688</v>
       </c>
       <c r="J13" t="n">
-        <v>39.03768920898438</v>
+        <v>45.34832382202148</v>
       </c>
       <c r="K13" t="n">
-        <v>28.12345314025879</v>
+        <v>28.08008766174316</v>
       </c>
     </row>
   </sheetData>

--- a/reports/nbeats_prediction_results.xlsx
+++ b/reports/nbeats_prediction_results.xlsx
@@ -511,19 +511,19 @@
         <v>23.4</v>
       </c>
       <c r="G2" t="n">
-        <v>39.58722686767578</v>
+        <v>56.30754852294922</v>
       </c>
       <c r="H2" t="n">
-        <v>59.52019119262695</v>
+        <v>56.48448944091797</v>
       </c>
       <c r="I2" t="n">
-        <v>2382.173828125</v>
+        <v>2537.248291015625</v>
       </c>
       <c r="J2" t="n">
-        <v>49.94996643066406</v>
+        <v>53.49288177490234</v>
       </c>
       <c r="K2" t="n">
-        <v>32.60894012451172</v>
+        <v>25.57209205627441</v>
       </c>
     </row>
     <row r="3">
@@ -546,19 +546,19 @@
         <v>23.5</v>
       </c>
       <c r="G3" t="n">
-        <v>58.1082763671875</v>
+        <v>51.93167877197266</v>
       </c>
       <c r="H3" t="n">
-        <v>67.18798828125</v>
+        <v>58.46515655517578</v>
       </c>
       <c r="I3" t="n">
-        <v>2227.640380859375</v>
+        <v>2845.19921875</v>
       </c>
       <c r="J3" t="n">
-        <v>49.80117416381836</v>
+        <v>42.52050399780273</v>
       </c>
       <c r="K3" t="n">
-        <v>28.94246864318848</v>
+        <v>26.82330894470215</v>
       </c>
     </row>
     <row r="4">
@@ -581,19 +581,19 @@
         <v>22.9</v>
       </c>
       <c r="G4" t="n">
-        <v>48.78900909423828</v>
+        <v>55.09148788452148</v>
       </c>
       <c r="H4" t="n">
-        <v>67.43144226074219</v>
+        <v>71.56495666503906</v>
       </c>
       <c r="I4" t="n">
-        <v>1837.168579101562</v>
+        <v>2703.04443359375</v>
       </c>
       <c r="J4" t="n">
-        <v>56.25993347167969</v>
+        <v>53.92378616333008</v>
       </c>
       <c r="K4" t="n">
-        <v>22.64511299133301</v>
+        <v>23.62313652038574</v>
       </c>
     </row>
     <row r="5">
@@ -616,19 +616,19 @@
         <v>22</v>
       </c>
       <c r="G5" t="n">
-        <v>52.79923629760742</v>
+        <v>41.64295196533203</v>
       </c>
       <c r="H5" t="n">
-        <v>76.94171905517578</v>
+        <v>60.08255004882812</v>
       </c>
       <c r="I5" t="n">
-        <v>2076.168212890625</v>
+        <v>1492.14697265625</v>
       </c>
       <c r="J5" t="n">
-        <v>62.34806442260742</v>
+        <v>49.16963958740234</v>
       </c>
       <c r="K5" t="n">
-        <v>30.45889091491699</v>
+        <v>33.14049911499023</v>
       </c>
     </row>
     <row r="6">
@@ -651,19 +651,19 @@
         <v>21</v>
       </c>
       <c r="G6" t="n">
-        <v>51.23588562011719</v>
+        <v>50.89614105224609</v>
       </c>
       <c r="H6" t="n">
-        <v>76.10706329345703</v>
+        <v>50.24392318725586</v>
       </c>
       <c r="I6" t="n">
-        <v>1296.419555664062</v>
+        <v>1496.43212890625</v>
       </c>
       <c r="J6" t="n">
-        <v>49.81579208374023</v>
+        <v>51.6594123840332</v>
       </c>
       <c r="K6" t="n">
-        <v>26.72619438171387</v>
+        <v>22.72770881652832</v>
       </c>
     </row>
     <row r="7">
@@ -686,19 +686,19 @@
         <v>20</v>
       </c>
       <c r="G7" t="n">
-        <v>57.15619659423828</v>
+        <v>43.86260986328125</v>
       </c>
       <c r="H7" t="n">
-        <v>76.60755920410156</v>
+        <v>78.82013702392578</v>
       </c>
       <c r="I7" t="n">
-        <v>1429.361572265625</v>
+        <v>1408.996826171875</v>
       </c>
       <c r="J7" t="n">
-        <v>43.31041717529297</v>
+        <v>49.2513313293457</v>
       </c>
       <c r="K7" t="n">
-        <v>19.55473899841309</v>
+        <v>22.03333854675293</v>
       </c>
     </row>
     <row r="8">
@@ -721,19 +721,19 @@
         <v>19</v>
       </c>
       <c r="G8" t="n">
-        <v>51.63566970825195</v>
+        <v>40.09001159667969</v>
       </c>
       <c r="H8" t="n">
-        <v>64.36302947998047</v>
+        <v>80.57546997070312</v>
       </c>
       <c r="I8" t="n">
-        <v>1273.521362304688</v>
+        <v>1672.991455078125</v>
       </c>
       <c r="J8" t="n">
-        <v>35.98403930664062</v>
+        <v>32.51483917236328</v>
       </c>
       <c r="K8" t="n">
-        <v>22.2281551361084</v>
+        <v>17.84552001953125</v>
       </c>
     </row>
     <row r="9">
@@ -756,19 +756,19 @@
         <v>18.6</v>
       </c>
       <c r="G9" t="n">
-        <v>55.3524169921875</v>
+        <v>46.63574600219727</v>
       </c>
       <c r="H9" t="n">
-        <v>50.62129592895508</v>
+        <v>65.00659942626953</v>
       </c>
       <c r="I9" t="n">
-        <v>839.0248413085938</v>
+        <v>857.9415283203125</v>
       </c>
       <c r="J9" t="n">
-        <v>38.55916595458984</v>
+        <v>40.97066879272461</v>
       </c>
       <c r="K9" t="n">
-        <v>18.53971481323242</v>
+        <v>13.71282196044922</v>
       </c>
     </row>
     <row r="10">
@@ -791,19 +791,19 @@
         <v>18.9</v>
       </c>
       <c r="G10" t="n">
-        <v>56.25220489501953</v>
+        <v>55.86869430541992</v>
       </c>
       <c r="H10" t="n">
-        <v>77.47187042236328</v>
+        <v>67.27167510986328</v>
       </c>
       <c r="I10" t="n">
-        <v>2057.587890625</v>
+        <v>1164.135620117188</v>
       </c>
       <c r="J10" t="n">
-        <v>46.10461044311523</v>
+        <v>26.83393478393555</v>
       </c>
       <c r="K10" t="n">
-        <v>14.25260543823242</v>
+        <v>22.10876274108887</v>
       </c>
     </row>
     <row r="11">
@@ -826,19 +826,19 @@
         <v>19.8</v>
       </c>
       <c r="G11" t="n">
-        <v>51.49188232421875</v>
+        <v>49.79767990112305</v>
       </c>
       <c r="H11" t="n">
-        <v>74.57093811035156</v>
+        <v>68.51962280273438</v>
       </c>
       <c r="I11" t="n">
-        <v>1267.251342773438</v>
+        <v>1709.052856445312</v>
       </c>
       <c r="J11" t="n">
-        <v>41.07585525512695</v>
+        <v>48.2940559387207</v>
       </c>
       <c r="K11" t="n">
-        <v>18.55783653259277</v>
+        <v>17.77501487731934</v>
       </c>
     </row>
     <row r="12">
@@ -861,19 +861,19 @@
         <v>24.2</v>
       </c>
       <c r="G12" t="n">
-        <v>54.42082214355469</v>
+        <v>44.44648742675781</v>
       </c>
       <c r="H12" t="n">
-        <v>67.63888549804688</v>
+        <v>70.60556793212891</v>
       </c>
       <c r="I12" t="n">
-        <v>1861.104858398438</v>
+        <v>1554.05078125</v>
       </c>
       <c r="J12" t="n">
-        <v>49.34075546264648</v>
+        <v>32.84084320068359</v>
       </c>
       <c r="K12" t="n">
-        <v>16.6522331237793</v>
+        <v>19.20673179626465</v>
       </c>
     </row>
     <row r="13">
@@ -896,19 +896,19 @@
         <v>30.8</v>
       </c>
       <c r="G13" t="n">
-        <v>52.6632080078125</v>
+        <v>66.50155639648438</v>
       </c>
       <c r="H13" t="n">
-        <v>58.63094329833984</v>
+        <v>55.25530624389648</v>
       </c>
       <c r="I13" t="n">
-        <v>1519.304565429688</v>
+        <v>892.3607177734375</v>
       </c>
       <c r="J13" t="n">
-        <v>45.34832382202148</v>
+        <v>39.03768920898438</v>
       </c>
       <c r="K13" t="n">
-        <v>28.08008766174316</v>
+        <v>28.12345314025879</v>
       </c>
     </row>
   </sheetData>
